--- a/cotacoes/2026-09-08/fechamento/PEDIDO_EPAN_MEDICAMENTOS_E_CRITICOS_10-09-2026.xlsx
+++ b/cotacoes/2026-09-08/fechamento/PEDIDO_EPAN_MEDICAMENTOS_E_CRITICOS_10-09-2026.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>EAN</t>
+          <t>EAN ePan (confirmado)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>7895858017422</t>
+          <t>7895858017439</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>7895858017309</t>
+          <t>7895858017415</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>000001355406</t>
+          <t>7891137003889</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -7809,6 +7809,7 @@
         <v/>
       </c>
     </row>
+    <row r="108"/>
     <row r="109">
       <c r="A109" s="14" t="inlineStr">
         <is>
